--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487561_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487561_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6644</v>
+        <v>5.7311</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7742</v>
+        <v>5.5626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8902</v>
+        <v>0.1685</v>
       </c>
       <c r="G2" t="n">
         <v>2.6494</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>3.757</v>
+        <v>1.8237</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1461</v>
+        <v>0.9345</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6109</v>
+        <v>0.8891</v>
       </c>
       <c r="V2" t="n">
         <v>2.4332</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6059</v>
+        <v>4.4503</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4885</v>
+        <v>6.119</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8826</v>
+        <v>-1.6688</v>
       </c>
       <c r="G3" t="n">
         <v>1.7997</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4691</v>
+        <v>0.3752</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3758</v>
+        <v>0.2547</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.1206</v>
       </c>
       <c r="V3" t="n">
         <v>1.492</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2299</v>
+        <v>2.1635</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9091</v>
+        <v>2.6021</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6792</v>
+        <v>-0.4386</v>
       </c>
       <c r="G4" t="n">
         <v>1.3545</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7591</v>
+        <v>0.6927</v>
       </c>
       <c r="T4" t="n">
-        <v>1.061</v>
+        <v>0.754</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3019</v>
+        <v>-0.0613</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3144</v>
+        <v>0.4656</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2643</v>
+        <v>4.469</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9499</v>
+        <v>-4.0034</v>
       </c>
       <c r="G5" t="n">
         <v>2.1948</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6531</v>
+        <v>0.8043</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7946</v>
+        <v>0.9992</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1415</v>
+        <v>-0.195</v>
       </c>
       <c r="V5" t="n">
         <v>-3.3169</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4147</v>
+        <v>0.0213</v>
       </c>
       <c r="E6" t="n">
-        <v>1.527</v>
+        <v>1.9363</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9417</v>
+        <v>-1.915</v>
       </c>
       <c r="G6" t="n">
         <v>-2.4734</v>
@@ -922,13 +922,13 @@
         <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1543</v>
+        <v>0.5903</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1588</v>
+        <v>0.5681</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0045</v>
+        <v>0.0222</v>
       </c>
       <c r="V6" t="n">
         <v>2.1003</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.0921</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0786</v>
+        <v>2.7945</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-2.8866</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0217</v>
+        <v>1.1823</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1096</v>
+        <v>0.2987</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1313</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0408</v>
+        <v>2.925</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0408</v>
+        <v>1.2487</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.6763</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0625</v>
+        <v>-1.7427</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0687</v>
+        <v>-0.9499</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1313</v>
+        <v>-0.7927</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.279</v>
+        <v>-0.4495</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2376</v>
+        <v>-0.4058</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0414</v>
+        <v>-0.0437</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3329</v>
+        <v>-1.2166</v>
       </c>
       <c r="W7" t="n">
         <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.711</v>
+        <v>-0.5208</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3093</v>
+        <v>0.138</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0202</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1823</v>
+        <v>-0.0217</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2987</v>
+        <v>0.1096</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.1313</v>
       </c>
       <c r="J8" t="n">
-        <v>2.925</v>
+        <v>0.0408</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2487</v>
+        <v>0.0408</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6763</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7427</v>
+        <v>-0.0625</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9499</v>
+        <v>0.0687</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7927</v>
+        <v>-0.1313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0683</v>
+        <v>-0.1661</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.891</v>
+        <v>-0.1782</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1773</v>
+        <v>0.0121</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W8" t="n">
         <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4284</v>
+        <v>-1.0944</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3655</v>
+        <v>-1.0849</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0629</v>
+        <v>-0.0095</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3483</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4925</v>
+        <v>-0.1585</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6952</v>
+        <v>-0.4146</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2027</v>
+        <v>0.2561</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5612</v>
+        <v>-2.6738</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5898</v>
+        <v>-0.6756</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9714</v>
+        <v>-1.9981</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1903</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1543</v>
+        <v>-0.2669</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2088</v>
+        <v>-0.2947</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0545</v>
+        <v>0.0278</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7013</v>
+        <v>-3.1953</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1684</v>
+        <v>-3.7426</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4671</v>
+        <v>0.5473</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1261</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5164</v>
+        <v>-0.0104</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.3882</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2975</v>
+        <v>0.3777</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3644</v>
+        <v>5.255400000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>17.2273</v>
+        <v>18.1184</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.8628</v>
+        <v>-12.863</v>
       </c>
       <c r="G12" t="n">
         <v>2.020899999999998</v>
@@ -1390,13 +1390,13 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3439</v>
+        <v>3.2348</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9381</v>
+        <v>1.829</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4057</v>
+        <v>1.4056</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>9.009499999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.009499999999999</v>
+        <v>-9.009499999999997</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8598</v>
+        <v>5.487</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2378</v>
+        <v>6.1588</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.378</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>2.0999</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2609</v>
+        <v>-0.6337</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6039</v>
+        <v>-0.6828</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6571</v>
+        <v>0.0491</v>
       </c>
       <c r="V13" t="n">
         <v>3.0415</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3465</v>
+        <v>1.0441</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0937</v>
+        <v>3.6843</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7471</v>
+        <v>-2.6402</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1245</v>
@@ -1624,13 +1624,13 @@
         <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6876</v>
+        <v>0.3852</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9069</v>
+        <v>0.4976</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2193</v>
+        <v>-0.1123</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5569</v>
+        <v>-0.4474</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9951</v>
+        <v>1.3637</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.552</v>
+        <v>-1.8112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4695</v>
+        <v>0.2083</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0401</v>
+        <v>-0.7972</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5706</v>
+        <v>1.0056</v>
       </c>
       <c r="J16" t="n">
-        <v>2.008</v>
+        <v>2.2989</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9224</v>
+        <v>0.3589</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0857</v>
+        <v>1.9399</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5385</v>
+        <v>-2.0905</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8822</v>
+        <v>-1.1562</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6563</v>
+        <v>-0.9344</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6234</v>
+        <v>0.3235</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0129</v>
+        <v>0.0441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6363</v>
+        <v>0.2794</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6521</v>
+        <v>-0.4699</v>
       </c>
       <c r="E17" t="n">
-        <v>1.159</v>
+        <v>1.224</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8112</v>
+        <v>-1.6939</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2083</v>
+        <v>-1.3262</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7972</v>
+        <v>0.3104</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0056</v>
+        <v>-1.6366</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2989</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3589</v>
+        <v>2.4821</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9399</v>
+        <v>-1.8042</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0905</v>
+        <v>-2.0041</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1562</v>
+        <v>-2.1717</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9344</v>
+        <v>0.1676</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9792</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1188</v>
+        <v>-0.5193</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1606</v>
+        <v>-0.4793</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2794</v>
+        <v>-0.04</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.9839</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7765</v>
+        <v>-0.71</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7467</v>
+        <v>1.8927</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5232</v>
+        <v>-2.6027</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7345</v>
+        <v>0.4695</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1605</v>
+        <v>1.0401</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8951</v>
+        <v>-0.5706</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5384</v>
+        <v>2.008</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0604</v>
+        <v>1.9224</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.522</v>
+        <v>0.0857</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2729</v>
+        <v>-1.5385</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8999</v>
+        <v>-0.8822</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.373</v>
+        <v>-0.6563</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9373</v>
+        <v>0.4704</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5585</v>
+        <v>-0.1153</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6212</v>
+        <v>0.5856</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6083</v>
+        <v>-2.4332</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5412</v>
+        <v>-1.3831</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0193</v>
+        <v>-0.379</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5605</v>
+        <v>-1.0041</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3262</v>
+        <v>-1.7345</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3104</v>
+        <v>1.1605</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6366</v>
+        <v>-2.8951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5384</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4821</v>
+        <v>3.0604</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8042</v>
+        <v>-2.522</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0041</v>
+        <v>-2.2729</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1717</v>
+        <v>-1.8999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1676</v>
+        <v>-0.373</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5906</v>
+        <v>0.3307</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.4329</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9065</v>
+        <v>-0.1022</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7673</v>
+        <v>0.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9839</v>
+        <v>0.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8391</v>
+        <v>-3.7414</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4347</v>
+        <v>-0.6394</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4044</v>
+        <v>-3.102</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1818</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3024</v>
+        <v>-0.2047</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4464</v>
+        <v>-0.6511</v>
       </c>
       <c r="U20" t="n">
-        <v>0.144</v>
+        <v>0.4464</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7673</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6258</v>
+        <v>-3.8356</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3967</v>
+        <v>-4.885</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7709</v>
+        <v>1.0494</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3859</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9069</v>
+        <v>-0.1167</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2892</v>
+        <v>-0.7775</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3823</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9412</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3645</v>
+        <v>-1.6355</v>
       </c>
       <c r="E22" t="n">
-        <v>12.8629</v>
+        <v>12.8628</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.2274</v>
+        <v>-14.4985</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.020700000000001</v>
+        <v>-2.0207</v>
       </c>
       <c r="H22" t="n">
-        <v>2.498001805406602e-16</v>
+        <v>4.718447854656915e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.020799999999999</v>
+        <v>-2.0208</v>
       </c>
       <c r="J22" t="n">
         <v>15.052</v>
@@ -2149,7 +2149,7 @@
         <v>12.5563</v>
       </c>
       <c r="L22" t="n">
-        <v>2.4954</v>
+        <v>2.495400000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-17.0725</v>
@@ -2164,22 +2164,22 @@
         <v>9.999999999993348e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>-9.792399999999999</v>
+        <v>-9.792400000000001</v>
       </c>
       <c r="R22" t="n">
         <v>9.792400000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3438</v>
+        <v>0.3853</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4058</v>
+        <v>-1.4056</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9379999999999998</v>
+        <v>1.7909</v>
       </c>
       <c r="V22" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="W22" t="n">
         <v>9.009399999999999</v>
